--- a/stock_tracker.xlsx
+++ b/stock_tracker.xlsx
@@ -508,7 +508,7 @@
         <v>46068</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
         <v>46066</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="4">
@@ -562,7 +562,7 @@
         <v>46052</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>23.1</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="5">
@@ -616,7 +616,7 @@
         <v>46058</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-2.3</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="7">
@@ -643,7 +643,7 @@
         <v>46050</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-1.7</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         <v>46058</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-3</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>46058</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-1.1</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="10">
@@ -724,7 +724,7 @@
         <v>46052</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-1.9</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="11">
@@ -751,7 +751,7 @@
         <v>46054</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-1.6</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="12">
@@ -778,7 +778,7 @@
         <v>46052</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="13">
@@ -805,7 +805,7 @@
         <v>46056</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.6</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="14">
@@ -832,7 +832,7 @@
         <v>46056</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-2.5</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="15">
@@ -859,7 +859,7 @@
         <v>46054</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-27.5</v>
+        <v>-27.46</v>
       </c>
     </row>
     <row r="16">
@@ -886,7 +886,7 @@
         <v>46052</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-3.4</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="17">
@@ -913,7 +913,7 @@
         <v>46066</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="18">
@@ -967,7 +967,7 @@
         <v>46054</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-2</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="20">
@@ -994,7 +994,7 @@
         <v>46062</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>7.3</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="21">
@@ -1021,7 +1021,7 @@
         <v>46058</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.8</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="22">
@@ -1048,7 +1048,7 @@
         <v>46058</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-2.9</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="23">
@@ -1075,7 +1075,7 @@
         <v>46068</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.8</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="24">
@@ -1102,7 +1102,7 @@
         <v>46058</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-2.6</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="25">
@@ -1129,7 +1129,7 @@
         <v>46068</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="26">
@@ -1156,7 +1156,7 @@
         <v>46066</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="27">
@@ -1183,7 +1183,7 @@
         <v>46066</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="28">
@@ -1237,7 +1237,7 @@
         <v>46066</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="30">
@@ -1264,7 +1264,7 @@
         <v>46066</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6.7</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="31">
@@ -1318,7 +1318,7 @@
         <v>46068</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="33">
@@ -1372,7 +1372,7 @@
         <v>46068</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="35">
@@ -1399,7 +1399,7 @@
         <v>46066</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="36">
@@ -1426,7 +1426,7 @@
         <v>46068</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-1.8</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="37">
@@ -1446,9 +1446,13 @@
       <c r="D37" s="3" t="n">
         <v>46068</v>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>876.6</v>
+      </c>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_tracker.xlsx
+++ b/stock_tracker.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recomendations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Trade_History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,13 +502,13 @@
         <v>46049</v>
       </c>
       <c r="E2" t="n">
-        <v>504.6</v>
+        <v>476</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46068</v>
+        <v>46100</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-1.29</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="3">
@@ -529,13 +529,13 @@
         <v>46049</v>
       </c>
       <c r="E3" t="n">
-        <v>93.16</v>
+        <v>91.66</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46066</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.98</v>
+        <v>46100</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="4">
@@ -556,13 +556,13 @@
         <v>46049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>46052</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>23.08</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="5">
@@ -583,13 +583,13 @@
         <v>46049</v>
       </c>
       <c r="E5" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46058</v>
+        <v>46100</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.2</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -610,13 +610,13 @@
         <v>46049</v>
       </c>
       <c r="E6" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>46058</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-2.27</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="7">
@@ -637,23 +637,23 @@
         <v>46049</v>
       </c>
       <c r="E7" t="n">
-        <v>53.91</v>
+        <v>60.23</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46050</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>-1.75</v>
+        <v>46089</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>9.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UPRO</t>
+          <t>NKHP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.64</v>
+        <v>550</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -664,23 +664,23 @@
         <v>46050</v>
       </c>
       <c r="E8" t="n">
-        <v>1.59</v>
+        <v>574</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>46058</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>-3.05</v>
+      <c r="G8" s="4" t="n">
+        <v>4.36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>NKHP</t>
+          <t>OZPH</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>550</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -691,23 +691,23 @@
         <v>46050</v>
       </c>
       <c r="E9" t="n">
-        <v>544</v>
+        <v>51.31</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>46058</v>
+        <v>46052</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-1.09</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OZPH</t>
+          <t>AKRN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>18674</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -718,23 +718,23 @@
         <v>46050</v>
       </c>
       <c r="E10" t="n">
-        <v>51.98</v>
+        <v>20844</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46052</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>-1.92</v>
+        <v>46100</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>11.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MOEX</t>
+          <t>PRFN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>185.68</v>
+        <v>4.44</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -745,23 +745,23 @@
         <v>46050</v>
       </c>
       <c r="E11" t="n">
-        <v>182.79</v>
+        <v>4.6</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>46054</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>-1.56</v>
+        <v>46056</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AKRN</t>
+          <t>RAGR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18674</v>
+        <v>123.52</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -772,23 +772,23 @@
         <v>46050</v>
       </c>
       <c r="E12" t="n">
-        <v>18438</v>
+        <v>118.48</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-1.26</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>PRFN</t>
+          <t>LNZLP</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.44</v>
+        <v>885</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -799,23 +799,23 @@
         <v>46050</v>
       </c>
       <c r="E13" t="n">
-        <v>4.69</v>
+        <v>242</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>5.63</v>
+        <v>46054</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-72.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>RAGR</t>
+          <t>KLSB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>123.52</v>
+        <v>22.85</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -826,131 +826,131 @@
         <v>46050</v>
       </c>
       <c r="E14" t="n">
-        <v>120.44</v>
+        <v>20.43</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>46056</v>
+        <v>46052</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-2.49</v>
+        <v>-10.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LNZLP</t>
+          <t>IVAT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>885</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Продажа</t>
+        <v>164.2</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Покупка</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46050</v>
+        <v>46053</v>
       </c>
       <c r="E15" t="n">
-        <v>642</v>
+        <v>152.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>46054</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>-27.46</v>
+        <v>46100</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-7.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>KLSB</t>
+          <t>MRKP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.85</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Продажа</t>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Покупка</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46050</v>
+        <v>46053</v>
       </c>
       <c r="E16" t="n">
-        <v>22.07</v>
+        <v>0.57</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-3.41</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>IVAT</t>
+          <t>CHMF</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>164.2</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Покупка</t>
+        <v>1010.2</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
         <v>46053</v>
       </c>
       <c r="E17" t="n">
-        <v>161.85</v>
+        <v>909.4</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>46066</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>-1.43</v>
+        <v>46054</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>-9.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>MRKP</t>
+          <t>MAGN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Покупка</t>
+        <v>30.65</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
         <v>46053</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5600000000000001</v>
+        <v>28.84</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46054</v>
+        <v>46062</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>-5.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CHMF</t>
+          <t>NLMK</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1010.2</v>
+        <v>114.16</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
@@ -961,23 +961,23 @@
         <v>46053</v>
       </c>
       <c r="E19" t="n">
-        <v>989.6</v>
+        <v>103</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46054</v>
+        <v>46058</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-2.04</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MAGN</t>
+          <t>KZOS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30.65</v>
+        <v>69.8</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -988,23 +988,23 @@
         <v>46053</v>
       </c>
       <c r="E20" t="n">
-        <v>32.88</v>
+        <v>68</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>46062</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>7.28</v>
+        <v>46058</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>NLMK</t>
+          <t>LSRG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>114.16</v>
+        <v>725.2</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1012,53 +1012,53 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46053</v>
+        <v>46056</v>
       </c>
       <c r="E21" t="n">
-        <v>113.22</v>
+        <v>717.6</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>46058</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.82</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>KZOS</t>
+          <t>SMLT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Продажа</t>
+        <v>856.2</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Покупка</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46053</v>
+        <v>46060</v>
       </c>
       <c r="E22" t="n">
-        <v>67.8</v>
+        <v>816.8</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>46058</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>-2.87</v>
+        <v>46070</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-4.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>FIXR</t>
+          <t>CNTL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.57</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -1066,53 +1066,53 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46055</v>
+        <v>46060</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5600000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>46068</v>
+        <v>46066</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.75</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSRG</t>
+          <t>MRKV</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>725.2</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Продажа</t>
+        <v>0.15</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Покупка</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46056</v>
+        <v>46065</v>
       </c>
       <c r="E24" t="n">
-        <v>706</v>
+        <v>0.17</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>46058</v>
+        <v>46066</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-2.65</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>SMLT</t>
+          <t>MRKC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>856.2</v>
+        <v>0.85</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -1120,53 +1120,53 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46060</v>
+        <v>46065</v>
       </c>
       <c r="E25" t="n">
-        <v>846.6</v>
+        <v>0.82</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>46068</v>
+        <v>46092</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.12</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CNTL</t>
+          <t>SVCB</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Покупка</t>
+        <v>13.58</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46060</v>
+        <v>46065</v>
       </c>
       <c r="E26" t="n">
-        <v>9.460000000000001</v>
+        <v>13.35</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>46066</v>
+        <v>46075</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1.07</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>SBER</t>
+          <t>CNTLP</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>302.05</v>
+        <v>6.06</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -1174,26 +1174,26 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46061</v>
+        <v>46066</v>
       </c>
       <c r="E27" t="n">
-        <v>308.55</v>
+        <v>5.97</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>46066</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>2.15</v>
+        <v>46100</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>TATN</t>
+          <t>IRAO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>546.9</v>
+        <v>3.44</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -1201,26 +1201,26 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="E28" t="n">
-        <v>546.9</v>
+        <v>3.21</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>46068</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>0</v>
+        <v>46096</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-6.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>SNGS</t>
+          <t>GEMC</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>21.89</v>
+        <v>876.6</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -1228,80 +1228,80 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46065</v>
+        <v>46068</v>
       </c>
       <c r="E29" t="n">
-        <v>21.95</v>
+        <v>864.9</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46066</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0.27</v>
+        <v>46077</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>MRKV</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Покупка</t>
+        <v>3492.8</v>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="E30" t="n">
-        <v>0.16</v>
+        <v>3355.8</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>46066</v>
+        <v>46075</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>6.67</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>MRKC</t>
+          <t>LSNGP</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Покупка</t>
+        <v>317.45</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="E31" t="n">
-        <v>0.85</v>
+        <v>321.65</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>46066</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>46082</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SVCB</t>
+          <t>MBNK</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13.58</v>
+        <v>1437.5</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -1309,26 +1309,24 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="E32" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>46068</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>2.28</v>
+        <v>1385.5</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" s="2" t="n">
+        <v>-3.62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>CNTLP</t>
+          <t>MDMG</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6.06</v>
+        <v>1462.4</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -1336,26 +1334,26 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="E33" t="n">
-        <v>6.06</v>
+        <v>1401.4</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>46068</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
+        <v>46100</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-4.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>BANE</t>
+          <t>VRSB</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1479.5</v>
+        <v>354.5</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -1363,43 +1361,43 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>46066</v>
+        <v>46084</v>
       </c>
       <c r="E34" t="n">
-        <v>1473</v>
+        <v>360</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>46068</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>-0.44</v>
+        <v>46086</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>IRAO</t>
+          <t>ROSN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Покупка</t>
+        <v>445.15</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>46066</v>
+        <v>46084</v>
       </c>
       <c r="E35" t="n">
-        <v>3.4</v>
+        <v>513.9</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>46066</v>
+        <v>46100</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.16</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="36">
@@ -1409,48 +1407,347 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>116.85</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Покупка</t>
+        <v>142.35</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>46066</v>
+        <v>46085</v>
       </c>
       <c r="E36" t="n">
-        <v>114.7</v>
+        <v>139.5</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>46068</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>-1.84</v>
+        <v>46092</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>GEMC</t>
+          <t>TATN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>876.6</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Покупка</t>
+        <v>621.4</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>46068</v>
+        <v>46085</v>
       </c>
       <c r="E37" t="n">
-        <v>876.6</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" s="2" t="n">
+        <v>652.8</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>BANE</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1734</v>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1705</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46094</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>FIXR</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>46086</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>-3.23</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>KAZT</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>448</v>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>46088</v>
+      </c>
+      <c r="E40" t="n">
+        <v>468.2</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>NVTK</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1345</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>46088</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1421.5</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>46096</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>GCHE</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3779</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>46088</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4066</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>MOEX</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>176.3</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>46088</v>
+      </c>
+      <c r="E43" t="n">
+        <v>173.46</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>UPRO</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>46088</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>134.61</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>46090</v>
+      </c>
+      <c r="E45" t="n">
+        <v>130.91</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="E46" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>-3.07</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>SOFL</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>46096</v>
+      </c>
+      <c r="E47" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>TATNP</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>606.4</v>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="E48" t="n">
+        <v>606.4</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>46100</v>
+      </c>
+      <c r="G48" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1465,7 +1762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,15 +1778,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Цена</t>
+          <t>Результат(%)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Результат(%)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Кол-во дней</t>
         </is>
@@ -1507,19 +1799,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.06</v>
+        <v>-3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="E2" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>BANE</t>
+          <t>IRAO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1528,34 +1817,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1479.5</v>
+        <v>-4.2</v>
       </c>
       <c r="D3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E3" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IRAO</t>
+          <t>SBER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Продажа</t>
+          <t>Покупка</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.44</v>
+        <v>4.63</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1566,17 +1849,122 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Продажа</t>
+          <t>Покупка</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>116.85</v>
+        <v>21.82</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>TATN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>BANE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>FIXR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="D8" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>MOEX</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>UPRO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Продажа</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-6.71</v>
+      </c>
+      <c r="D10" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SNGS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Покупка</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
